--- a/Team-Data/2009-10/4-9-2009-10.xlsx
+++ b/Team-Data/2009-10/4-9-2009-10.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -676,49 +743,49 @@
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="J2" t="n">
         <v>83.2</v>
       </c>
       <c r="K2" t="n">
-        <v>0.464</v>
+        <v>0.466</v>
       </c>
       <c r="L2" t="n">
         <v>6.4</v>
       </c>
       <c r="M2" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="N2" t="n">
-        <v>0.357</v>
+        <v>0.36</v>
       </c>
       <c r="O2" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P2" t="n">
         <v>23.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.76</v>
+        <v>0.757</v>
       </c>
       <c r="R2" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T2" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U2" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="V2" t="n">
         <v>11.9</v>
       </c>
       <c r="W2" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X2" t="n">
         <v>4.9</v>
@@ -730,16 +797,16 @@
         <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.4</v>
+        <v>101.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
@@ -751,13 +818,13 @@
         <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK2" t="n">
         <v>11</v>
@@ -772,22 +839,22 @@
         <v>11</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
         <v>10</v>
@@ -796,10 +863,10 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -843,55 +910,55 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.61</v>
+        <v>0.628</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J3" t="n">
-        <v>76.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.345</v>
+        <v>0.347</v>
       </c>
       <c r="O3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>25.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.742</v>
+        <v>0.745</v>
       </c>
       <c r="R3" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T3" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="U3" t="n">
         <v>23.7</v>
@@ -900,7 +967,7 @@
         <v>15.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
         <v>4.9</v>
@@ -912,25 +979,25 @@
         <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>99.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AD3" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="AE3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH3" t="n">
         <v>17</v>
@@ -951,7 +1018,7 @@
         <v>16</v>
       </c>
       <c r="AN3" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO3" t="n">
         <v>15</v>
@@ -960,13 +1027,13 @@
         <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
@@ -975,13 +1042,13 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW3" t="n">
         <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
         <v>15</v>
@@ -990,13 +1057,13 @@
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
         <v>19</v>
       </c>
       <c r="BC3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1040,31 +1107,31 @@
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>34.9</v>
+        <v>34.8</v>
       </c>
       <c r="J4" t="n">
         <v>76.90000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L4" t="n">
         <v>5.7</v>
       </c>
       <c r="M4" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.348</v>
+        <v>0.346</v>
       </c>
       <c r="O4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="P4" t="n">
         <v>26.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.747</v>
       </c>
       <c r="R4" t="n">
         <v>10.5</v>
@@ -1076,10 +1143,10 @@
         <v>40.9</v>
       </c>
       <c r="U4" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V4" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.7</v>
@@ -1094,16 +1161,16 @@
         <v>19.4</v>
       </c>
       <c r="AA4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB4" t="n">
-        <v>95.7</v>
+        <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE4" t="n">
         <v>15</v>
@@ -1115,7 +1182,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1124,7 +1191,7 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>21</v>
@@ -1133,10 +1200,10 @@
         <v>22</v>
       </c>
       <c r="AN4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>4</v>
@@ -1145,7 +1212,7 @@
         <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>19</v>
@@ -1154,7 +1221,7 @@
         <v>22</v>
       </c>
       <c r="AU4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
         <v>29</v>
@@ -1163,7 +1230,7 @@
         <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1175,10 +1242,10 @@
         <v>6</v>
       </c>
       <c r="BB4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1207,55 +1274,55 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E5" t="n">
         <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>0.481</v>
+        <v>0.487</v>
       </c>
       <c r="H5" t="n">
-        <v>48.6</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J5" t="n">
-        <v>83.3</v>
+        <v>83.2</v>
       </c>
       <c r="K5" t="n">
         <v>0.45</v>
       </c>
       <c r="L5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M5" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.331</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="P5" t="n">
         <v>23.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.754</v>
+        <v>0.756</v>
       </c>
       <c r="R5" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>44.5</v>
+        <v>44.4</v>
       </c>
       <c r="U5" t="n">
         <v>20.7</v>
@@ -1276,16 +1343,16 @@
         <v>20.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>97.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.1</v>
+        <v>-2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1297,7 +1364,7 @@
         <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>17</v>
@@ -1324,7 +1391,7 @@
         <v>19</v>
       </c>
       <c r="AQ5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>12</v>
@@ -1339,7 +1406,7 @@
         <v>19</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW5" t="n">
         <v>23</v>
@@ -1351,13 +1418,13 @@
         <v>24</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA5" t="n">
         <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>18</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E6" t="n">
         <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" t="n">
-        <v>0.782</v>
+        <v>0.772</v>
       </c>
       <c r="H6" t="n">
         <v>48.3</v>
       </c>
       <c r="I6" t="n">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="J6" t="n">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.49</v>
+        <v>0.487</v>
       </c>
       <c r="L6" t="n">
         <v>7.4</v>
@@ -1422,13 +1489,13 @@
         <v>0.384</v>
       </c>
       <c r="O6" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P6" t="n">
-        <v>26.3</v>
+        <v>26.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.722</v>
+        <v>0.72</v>
       </c>
       <c r="R6" t="n">
         <v>9.6</v>
@@ -1437,37 +1504,37 @@
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U6" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="V6" t="n">
         <v>13.8</v>
       </c>
       <c r="W6" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X6" t="n">
         <v>5.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>102.8</v>
+        <v>102.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1479,13 +1546,13 @@
         <v>1</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
@@ -1494,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="AM6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN6" t="n">
         <v>2</v>
@@ -1506,10 +1573,10 @@
         <v>7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR6" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS6" t="n">
         <v>2</v>
@@ -1518,7 +1585,7 @@
         <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1542,7 +1609,7 @@
         <v>7</v>
       </c>
       <c r="BC6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1574,25 +1641,25 @@
         <v>78</v>
       </c>
       <c r="E7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
-        <v>0.667</v>
+        <v>0.654</v>
       </c>
       <c r="H7" t="n">
         <v>48.5</v>
       </c>
       <c r="I7" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J7" t="n">
-        <v>82.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.464</v>
+        <v>0.465</v>
       </c>
       <c r="L7" t="n">
         <v>6.7</v>
@@ -1601,16 +1668,16 @@
         <v>18.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.37</v>
+        <v>0.369</v>
       </c>
       <c r="O7" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P7" t="n">
         <v>22.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>10.2</v>
@@ -1631,37 +1698,37 @@
         <v>7.6</v>
       </c>
       <c r="X7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z7" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="AD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE7" t="n">
         <v>5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>4</v>
       </c>
       <c r="AF7" t="n">
         <v>4</v>
       </c>
       <c r="AG7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH7" t="n">
         <v>4</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>5</v>
       </c>
       <c r="AI7" t="n">
         <v>9</v>
@@ -1697,7 +1764,7 @@
         <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
         <v>4</v>
@@ -1709,22 +1776,22 @@
         <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="n">
         <v>27</v>
       </c>
       <c r="G8" t="n">
-        <v>0.654</v>
+        <v>0.658</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J8" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.469</v>
@@ -1780,7 +1847,7 @@
         <v>6.6</v>
       </c>
       <c r="M8" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="N8" t="n">
         <v>0.36</v>
@@ -1795,7 +1862,7 @@
         <v>0.774</v>
       </c>
       <c r="R8" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
@@ -1810,7 +1877,7 @@
         <v>14</v>
       </c>
       <c r="W8" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X8" t="n">
         <v>5</v>
@@ -1822,31 +1889,31 @@
         <v>22.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.5</v>
+        <v>106.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
         <v>17</v>
@@ -1861,7 +1928,7 @@
         <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,10 +1937,10 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>15</v>
@@ -1882,7 +1949,7 @@
         <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV8" t="n">
         <v>12</v>
@@ -1897,7 +1964,7 @@
         <v>23</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -1953,7 +2020,7 @@
         <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K9" t="n">
         <v>0.444</v>
@@ -1962,28 +2029,28 @@
         <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.315</v>
+        <v>0.314</v>
       </c>
       <c r="O9" t="n">
         <v>17.7</v>
       </c>
       <c r="P9" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.731</v>
+        <v>0.727</v>
       </c>
       <c r="R9" t="n">
         <v>12.9</v>
       </c>
       <c r="S9" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="T9" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U9" t="n">
         <v>19.3</v>
@@ -2001,19 +2068,19 @@
         <v>4.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.8</v>
+        <v>93.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE9" t="n">
         <v>25</v>
@@ -2025,7 +2092,7 @@
         <v>25</v>
       </c>
       <c r="AH9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI9" t="n">
         <v>28</v>
@@ -2040,16 +2107,16 @@
         <v>28</v>
       </c>
       <c r="AM9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN9" t="n">
         <v>30</v>
       </c>
       <c r="AO9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9" t="n">
         <v>27</v>
@@ -2070,16 +2137,16 @@
         <v>9</v>
       </c>
       <c r="AW9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AX9" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY9" t="n">
         <v>16</v>
       </c>
       <c r="AZ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>0.312</v>
+        <v>0.308</v>
       </c>
       <c r="H10" t="n">
         <v>48.1</v>
@@ -2141,34 +2208,34 @@
         <v>0.47</v>
       </c>
       <c r="L10" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M10" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N10" t="n">
         <v>0.372</v>
       </c>
       <c r="O10" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P10" t="n">
         <v>25.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.785</v>
+        <v>0.783</v>
       </c>
       <c r="R10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S10" t="n">
         <v>29.1</v>
       </c>
       <c r="T10" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="U10" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="V10" t="n">
         <v>14.8</v>
@@ -2189,19 +2256,19 @@
         <v>21.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.8</v>
+        <v>108.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
       </c>
       <c r="AF10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG10" t="n">
         <v>27</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL10" t="n">
         <v>7</v>
@@ -2228,7 +2295,7 @@
         <v>4</v>
       </c>
       <c r="AO10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP10" t="n">
         <v>11</v>
@@ -2246,10 +2313,10 @@
         <v>30</v>
       </c>
       <c r="AU10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2366,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E11" t="n">
         <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>0.519</v>
+        <v>0.513</v>
       </c>
       <c r="H11" t="n">
         <v>48.6</v>
       </c>
       <c r="I11" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J11" t="n">
         <v>84.40000000000001</v>
@@ -2326,16 +2393,16 @@
         <v>7.8</v>
       </c>
       <c r="M11" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N11" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="O11" t="n">
         <v>19.1</v>
       </c>
       <c r="P11" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0.771</v>
@@ -2344,28 +2411,28 @@
         <v>12</v>
       </c>
       <c r="S11" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T11" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="U11" t="n">
         <v>21.6</v>
       </c>
       <c r="V11" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W11" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X11" t="n">
         <v>3.8</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA11" t="n">
         <v>22.5</v>
@@ -2374,10 +2441,10 @@
         <v>102.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>16</v>
@@ -2407,10 +2474,10 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP11" t="n">
         <v>13</v>
@@ -2422,7 +2489,7 @@
         <v>3</v>
       </c>
       <c r="AS11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT11" t="n">
         <v>12</v>
@@ -2434,16 +2501,16 @@
         <v>17</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AX11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY11" t="n">
         <v>30</v>
       </c>
       <c r="AZ11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
         <v>2</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -2484,13 +2551,13 @@
         <v>78</v>
       </c>
       <c r="E12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G12" t="n">
-        <v>0.397</v>
+        <v>0.385</v>
       </c>
       <c r="H12" t="n">
         <v>48.1</v>
@@ -2499,67 +2566,67 @@
         <v>36.7</v>
       </c>
       <c r="J12" t="n">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L12" t="n">
         <v>8</v>
       </c>
       <c r="M12" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="N12" t="n">
         <v>0.348</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P12" t="n">
         <v>24.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.773</v>
+        <v>0.775</v>
       </c>
       <c r="R12" t="n">
         <v>9.6</v>
       </c>
       <c r="S12" t="n">
-        <v>32.1</v>
+        <v>32.2</v>
       </c>
       <c r="T12" t="n">
         <v>41.7</v>
       </c>
       <c r="U12" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V12" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W12" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X12" t="n">
         <v>5.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA12" t="n">
         <v>20.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>100.6</v>
+        <v>100.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.9</v>
+        <v>-3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,13 +2638,13 @@
         <v>21</v>
       </c>
       <c r="AH12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI12" t="n">
         <v>22</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
         <v>13</v>
@@ -2598,34 +2665,34 @@
         <v>14</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS12" t="n">
         <v>5</v>
       </c>
       <c r="AT12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU12" t="n">
         <v>17</v>
       </c>
-      <c r="AU12" t="n">
-        <v>16</v>
-      </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
         <v>14</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E13" t="n">
         <v>27</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>0.351</v>
+        <v>0.342</v>
       </c>
       <c r="H13" t="n">
         <v>48.1</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J13" t="n">
         <v>80.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L13" t="n">
         <v>5.9</v>
       </c>
       <c r="M13" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.332</v>
+        <v>0.331</v>
       </c>
       <c r="O13" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P13" t="n">
         <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="R13" t="n">
         <v>11.4</v>
@@ -2714,13 +2781,13 @@
         <v>41.6</v>
       </c>
       <c r="U13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V13" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="W13" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X13" t="n">
         <v>5.7</v>
@@ -2729,25 +2796,25 @@
         <v>4.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
@@ -2756,13 +2823,13 @@
         <v>29</v>
       </c>
       <c r="AI13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
         <v>20</v>
@@ -2774,7 +2841,7 @@
         <v>27</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP13" t="n">
         <v>25</v>
@@ -2786,7 +2853,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT13" t="n">
         <v>19</v>
@@ -2804,16 +2871,16 @@
         <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA13" t="n">
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -2866,25 +2933,25 @@
         <v>83.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.459</v>
+        <v>0.458</v>
       </c>
       <c r="L14" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
         <v>19.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.343</v>
+        <v>0.342</v>
       </c>
       <c r="O14" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P14" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
         <v>11.7</v>
@@ -2893,10 +2960,10 @@
         <v>32.6</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V14" t="n">
         <v>13.4</v>
@@ -2905,7 +2972,7 @@
         <v>7.6</v>
       </c>
       <c r="X14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y14" t="n">
         <v>4.4</v>
@@ -2914,7 +2981,7 @@
         <v>19.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB14" t="n">
         <v>102</v>
@@ -2923,7 +2990,7 @@
         <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2938,7 +3005,7 @@
         <v>11</v>
       </c>
       <c r="AI14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ14" t="n">
         <v>8</v>
@@ -2953,13 +3020,13 @@
         <v>10</v>
       </c>
       <c r="AN14" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>16</v>
       </c>
       <c r="AP14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ14" t="n">
         <v>12</v>
@@ -2977,16 +3044,16 @@
         <v>15</v>
       </c>
       <c r="AV14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
         <v>6</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3030,43 +3097,43 @@
         <v>78</v>
       </c>
       <c r="E15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" t="n">
-        <v>0.513</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>39.6</v>
+        <v>39.4</v>
       </c>
       <c r="J15" t="n">
-        <v>84.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L15" t="n">
         <v>4.3</v>
       </c>
       <c r="M15" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.344</v>
+        <v>0.341</v>
       </c>
       <c r="O15" t="n">
         <v>19.4</v>
       </c>
       <c r="P15" t="n">
-        <v>26.4</v>
+        <v>26.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R15" t="n">
         <v>13.1</v>
@@ -3078,10 +3145,10 @@
         <v>43.6</v>
       </c>
       <c r="U15" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>7.9</v>
@@ -3090,25 +3157,25 @@
         <v>4.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA15" t="n">
         <v>22.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.9</v>
+        <v>102.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.7</v>
+        <v>-1.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF15" t="n">
         <v>17</v>
@@ -3117,16 +3184,16 @@
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL15" t="n">
         <v>29</v>
@@ -3135,7 +3202,7 @@
         <v>30</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO15" t="n">
         <v>9</v>
@@ -3150,7 +3217,7 @@
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
         <v>3</v>
@@ -3165,7 +3232,7 @@
         <v>7</v>
       </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3212,25 +3279,25 @@
         <v>78</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G16" t="n">
-        <v>0.551</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="K16" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L16" t="n">
         <v>6</v>
@@ -3239,7 +3306,7 @@
         <v>17.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.345</v>
+        <v>0.346</v>
       </c>
       <c r="O16" t="n">
         <v>17.8</v>
@@ -3251,13 +3318,13 @@
         <v>0.751</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S16" t="n">
-        <v>31.1</v>
+        <v>31.3</v>
       </c>
       <c r="T16" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U16" t="n">
         <v>18.9</v>
@@ -3269,34 +3336,34 @@
         <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>4.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA16" t="n">
         <v>20.1</v>
       </c>
       <c r="AB16" t="n">
-        <v>96</v>
+        <v>96.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
         <v>11</v>
@@ -3305,10 +3372,10 @@
         <v>27</v>
       </c>
       <c r="AJ16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>17</v>
@@ -3317,7 +3384,7 @@
         <v>17</v>
       </c>
       <c r="AN16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>19</v>
@@ -3329,13 +3396,13 @@
         <v>19</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS16" t="n">
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>28</v>
@@ -3350,19 +3417,19 @@
         <v>4</v>
       </c>
       <c r="AY16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F17" t="n">
         <v>34</v>
       </c>
       <c r="G17" t="n">
-        <v>0.57</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H17" t="n">
         <v>48.8</v>
@@ -3409,7 +3476,7 @@
         <v>37.3</v>
       </c>
       <c r="J17" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="K17" t="n">
         <v>0.436</v>
@@ -3418,19 +3485,19 @@
         <v>7.8</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="N17" t="n">
         <v>0.356</v>
       </c>
       <c r="O17" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="P17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.755</v>
+        <v>0.752</v>
       </c>
       <c r="R17" t="n">
         <v>11.8</v>
@@ -3457,7 +3524,7 @@
         <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA17" t="n">
         <v>20.2</v>
@@ -3469,7 +3536,7 @@
         <v>1.9</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE17" t="n">
         <v>13</v>
@@ -3508,13 +3575,13 @@
         <v>29</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT17" t="n">
         <v>6</v>
@@ -3523,28 +3590,28 @@
         <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>19</v>
       </c>
       <c r="AY17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
         <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3576,61 +3643,61 @@
         <v>78</v>
       </c>
       <c r="E18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>0.179</v>
+        <v>0.192</v>
       </c>
       <c r="H18" t="n">
         <v>48.3</v>
       </c>
       <c r="I18" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J18" t="n">
         <v>84.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.45</v>
+        <v>0.449</v>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="M18" t="n">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O18" t="n">
-        <v>17.1</v>
+        <v>17.4</v>
       </c>
       <c r="P18" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S18" t="n">
         <v>31.3</v>
       </c>
       <c r="T18" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U18" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V18" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
@@ -3642,16 +3709,16 @@
         <v>20.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-9.4</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3663,10 +3730,10 @@
         <v>29</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ18" t="n">
         <v>3</v>
@@ -3675,7 +3742,7 @@
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM18" t="n">
         <v>26</v>
@@ -3687,13 +3754,13 @@
         <v>25</v>
       </c>
       <c r="AP18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
         <v>12</v>
@@ -3708,7 +3775,7 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>20</v>
       </c>
       <c r="BC18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3758,34 +3825,34 @@
         <v>78</v>
       </c>
       <c r="E19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G19" t="n">
-        <v>0.154</v>
+        <v>0.141</v>
       </c>
       <c r="H19" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J19" t="n">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="K19" t="n">
         <v>0.429</v>
       </c>
       <c r="L19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M19" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.326</v>
+        <v>0.325</v>
       </c>
       <c r="O19" t="n">
         <v>19.1</v>
@@ -3794,7 +3861,7 @@
         <v>24.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.781</v>
       </c>
       <c r="R19" t="n">
         <v>10.8</v>
@@ -3809,31 +3876,31 @@
         <v>18.8</v>
       </c>
       <c r="V19" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="W19" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="n">
         <v>20.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.3</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>30</v>
@@ -3845,13 +3912,13 @@
         <v>30</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
       </c>
       <c r="AJ19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK19" t="n">
         <v>30</v>
@@ -3866,13 +3933,13 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AP19" t="n">
         <v>15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR19" t="n">
         <v>18</v>
@@ -3887,28 +3954,28 @@
         <v>29</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY19" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB19" t="n">
         <v>30</v>
       </c>
       <c r="BC19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -3964,10 +4031,10 @@
         <v>7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.361</v>
+        <v>0.36</v>
       </c>
       <c r="O20" t="n">
         <v>15.7</v>
@@ -3976,7 +4043,7 @@
         <v>20.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R20" t="n">
         <v>10.5</v>
@@ -4009,10 +4076,10 @@
         <v>19.4</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.8</v>
+        <v>-2.9</v>
       </c>
       <c r="AD20" t="n">
         <v>1</v>
@@ -4036,16 +4103,16 @@
         <v>9</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
       </c>
       <c r="AM20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4054,10 +4121,10 @@
         <v>30</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4066,10 +4133,10 @@
         <v>26</v>
       </c>
       <c r="AU20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>9</v>
@@ -4078,7 +4145,7 @@
         <v>30</v>
       </c>
       <c r="AY20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -4137,19 +4204,19 @@
         <v>38.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M21" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.346</v>
+        <v>0.342</v>
       </c>
       <c r="O21" t="n">
         <v>16.6</v>
@@ -4158,7 +4225,7 @@
         <v>21.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.779</v>
+        <v>0.78</v>
       </c>
       <c r="R21" t="n">
         <v>10.1</v>
@@ -4170,7 +4237,7 @@
         <v>40.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V21" t="n">
         <v>14</v>
@@ -4185,19 +4252,19 @@
         <v>4.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>19.2</v>
       </c>
       <c r="AB21" t="n">
-        <v>102</v>
+        <v>101.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.5</v>
+        <v>-3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE21" t="n">
         <v>22</v>
@@ -4209,16 +4276,16 @@
         <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI21" t="n">
         <v>12</v>
       </c>
       <c r="AJ21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL21" t="n">
         <v>2</v>
@@ -4227,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO21" t="n">
         <v>28</v>
@@ -4245,22 +4312,22 @@
         <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU21" t="n">
         <v>12</v>
       </c>
       <c r="AV21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
         <v>15</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ21" t="n">
         <v>9</v>
@@ -4269,7 +4336,7 @@
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -4319,34 +4386,34 @@
         <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.461</v>
+        <v>0.463</v>
       </c>
       <c r="L22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="M22" t="n">
         <v>14.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.334</v>
+        <v>0.337</v>
       </c>
       <c r="O22" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q22" t="n">
         <v>0.805</v>
       </c>
       <c r="R22" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S22" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T22" t="n">
         <v>43.5</v>
@@ -4358,10 +4425,10 @@
         <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X22" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y22" t="n">
         <v>4.7</v>
@@ -4370,25 +4437,25 @@
         <v>21.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AB22" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4400,16 +4467,16 @@
         <v>20</v>
       </c>
       <c r="AK22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM22" t="n">
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -4424,16 +4491,16 @@
         <v>10</v>
       </c>
       <c r="AS22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
         <v>4</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW22" t="n">
         <v>6</v>
@@ -4454,7 +4521,7 @@
         <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -4498,10 +4565,10 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>77.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="K23" t="n">
         <v>0.467</v>
@@ -4513,19 +4580,19 @@
         <v>27.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.372</v>
+        <v>0.373</v>
       </c>
       <c r="O23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P23" t="n">
         <v>26.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S23" t="n">
         <v>33.4</v>
@@ -4537,16 +4604,16 @@
         <v>19.4</v>
       </c>
       <c r="V23" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="W23" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X23" t="n">
         <v>5.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z23" t="n">
         <v>19.9</v>
@@ -4561,7 +4628,7 @@
         <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>2</v>
@@ -4573,13 +4640,13 @@
         <v>2</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
         <v>10</v>
@@ -4600,7 +4667,7 @@
         <v>5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
@@ -4636,7 +4703,7 @@
         <v>8</v>
       </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -4692,34 +4759,34 @@
         <v>5.6</v>
       </c>
       <c r="M24" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="N24" t="n">
         <v>0.336</v>
       </c>
       <c r="O24" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P24" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.758</v>
+        <v>0.761</v>
       </c>
       <c r="R24" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S24" t="n">
         <v>29.7</v>
       </c>
       <c r="T24" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="U24" t="n">
         <v>20.7</v>
       </c>
       <c r="V24" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W24" t="n">
         <v>8.199999999999999</v>
@@ -4737,19 +4804,19 @@
         <v>18.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>97.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>24</v>
       </c>
       <c r="AF24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG24" t="n">
         <v>24</v>
@@ -4761,7 +4828,7 @@
         <v>18</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
         <v>17</v>
@@ -4773,16 +4840,16 @@
         <v>21</v>
       </c>
       <c r="AN24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP24" t="n">
         <v>27</v>
       </c>
       <c r="AQ24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
         <v>11</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC24" t="n">
         <v>24</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -4850,40 +4917,40 @@
         <v>78</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G25" t="n">
-        <v>0.641</v>
+        <v>0.654</v>
       </c>
       <c r="H25" t="n">
         <v>48.1</v>
       </c>
       <c r="I25" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="J25" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K25" t="n">
-        <v>0.491</v>
+        <v>0.492</v>
       </c>
       <c r="L25" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.409</v>
+        <v>0.41</v>
       </c>
       <c r="O25" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="P25" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q25" t="n">
         <v>0.773</v>
@@ -4892,16 +4959,16 @@
         <v>11.2</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
-        <v>43.1</v>
+        <v>42.9</v>
       </c>
       <c r="U25" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V25" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W25" t="n">
         <v>5.8</v>
@@ -4919,25 +4986,25 @@
         <v>21.7</v>
       </c>
       <c r="AB25" t="n">
-        <v>110.1</v>
+        <v>110.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AD25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE25" t="n">
         <v>5</v>
       </c>
-      <c r="AE25" t="n">
-        <v>7</v>
-      </c>
       <c r="AF25" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>1</v>
@@ -4946,7 +5013,7 @@
         <v>13</v>
       </c>
       <c r="AK25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL25" t="n">
         <v>3</v>
@@ -4958,7 +5025,7 @@
         <v>1</v>
       </c>
       <c r="AO25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP25" t="n">
         <v>9</v>
@@ -4970,7 +5037,7 @@
         <v>15</v>
       </c>
       <c r="AS25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -4979,7 +5046,7 @@
         <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW25" t="n">
         <v>29</v>
@@ -4988,10 +5055,10 @@
         <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>7</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5032,13 +5099,13 @@
         <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="n">
-        <v>0.603</v>
+        <v>0.615</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5050,16 +5117,16 @@
         <v>78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
         <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.352</v>
+        <v>0.356</v>
       </c>
       <c r="O26" t="n">
         <v>19.7</v>
@@ -5068,28 +5135,28 @@
         <v>24.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.792</v>
       </c>
       <c r="R26" t="n">
         <v>11.2</v>
       </c>
       <c r="S26" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T26" t="n">
-        <v>40</v>
+        <v>40.1</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.2</v>
+        <v>12.4</v>
       </c>
       <c r="W26" t="n">
         <v>6.5</v>
       </c>
       <c r="X26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y26" t="n">
         <v>4.1</v>
@@ -5098,28 +5165,28 @@
         <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.90000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
         <v>10</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>26</v>
@@ -5131,7 +5198,7 @@
         <v>15</v>
       </c>
       <c r="AL26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM26" t="n">
         <v>20</v>
@@ -5173,7 +5240,7 @@
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5211,61 +5278,61 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G27" t="n">
-        <v>0.321</v>
+        <v>0.316</v>
       </c>
       <c r="H27" t="n">
         <v>48.5</v>
       </c>
       <c r="I27" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="J27" t="n">
-        <v>84.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="K27" t="n">
-        <v>0.456</v>
+        <v>0.455</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M27" t="n">
         <v>17</v>
       </c>
       <c r="N27" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O27" t="n">
         <v>17.4</v>
       </c>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.723</v>
+        <v>0.724</v>
       </c>
       <c r="R27" t="n">
         <v>11.9</v>
       </c>
       <c r="S27" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T27" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U27" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V27" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W27" t="n">
         <v>6.8</v>
@@ -5283,43 +5350,43 @@
         <v>20.2</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="AC27" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
       </c>
       <c r="AF27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ27" t="n">
         <v>6</v>
       </c>
       <c r="AK27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>19</v>
       </c>
       <c r="AN27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AO27" t="n">
         <v>24</v>
@@ -5328,10 +5395,10 @@
         <v>18</v>
       </c>
       <c r="AQ27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS27" t="n">
         <v>14</v>
@@ -5343,7 +5410,7 @@
         <v>20</v>
       </c>
       <c r="AV27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AW27" t="n">
         <v>22</v>
@@ -5355,10 +5422,10 @@
         <v>27</v>
       </c>
       <c r="AZ27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5396,46 +5463,46 @@
         <v>78</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F28" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" t="n">
-        <v>0.603</v>
+        <v>0.615</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L28" t="n">
         <v>6.7</v>
       </c>
       <c r="M28" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.359</v>
+        <v>0.36</v>
       </c>
       <c r="O28" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="P28" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="Q28" t="n">
         <v>0.745</v>
       </c>
       <c r="R28" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S28" t="n">
         <v>31.8</v>
@@ -5444,16 +5511,16 @@
         <v>42.7</v>
       </c>
       <c r="U28" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V28" t="n">
         <v>13.6</v>
       </c>
       <c r="W28" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y28" t="n">
         <v>5.1</v>
@@ -5462,31 +5529,31 @@
         <v>20.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>100.9</v>
+        <v>101.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AD28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE28" t="n">
         <v>10</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>18</v>
@@ -5495,13 +5562,13 @@
         <v>6</v>
       </c>
       <c r="AL28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM28" t="n">
         <v>11</v>
       </c>
       <c r="AN28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO28" t="n">
         <v>23</v>
@@ -5510,7 +5577,7 @@
         <v>21</v>
       </c>
       <c r="AQ28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR28" t="n">
         <v>16</v>
@@ -5522,31 +5589,31 @@
         <v>10</v>
       </c>
       <c r="AU28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>10</v>
       </c>
       <c r="AW28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY28" t="n">
         <v>20</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>21</v>
       </c>
       <c r="AZ28" t="n">
         <v>13</v>
       </c>
       <c r="BA28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>15</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5578,22 +5645,22 @@
         <v>78</v>
       </c>
       <c r="E29" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" t="n">
-        <v>0.474</v>
+        <v>0.487</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>38.9</v>
+        <v>38.7</v>
       </c>
       <c r="J29" t="n">
-        <v>80.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="K29" t="n">
         <v>0.48</v>
@@ -5605,34 +5672,34 @@
         <v>17.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O29" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="P29" t="n">
-        <v>26</v>
+        <v>26.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.765</v>
+        <v>0.766</v>
       </c>
       <c r="R29" t="n">
         <v>10</v>
       </c>
       <c r="S29" t="n">
-        <v>30.4</v>
+        <v>30.6</v>
       </c>
       <c r="T29" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="U29" t="n">
         <v>21.7</v>
       </c>
       <c r="V29" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="W29" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="X29" t="n">
         <v>4.7</v>
@@ -5641,34 +5708,34 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB29" t="n">
         <v>103.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.2</v>
+        <v>-2</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ29" t="n">
         <v>19</v>
@@ -5686,7 +5753,7 @@
         <v>5</v>
       </c>
       <c r="AO29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP29" t="n">
         <v>8</v>
@@ -5698,13 +5765,13 @@
         <v>25</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV29" t="n">
         <v>8</v>
@@ -5713,13 +5780,13 @@
         <v>30</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA29" t="n">
         <v>12</v>
@@ -5728,7 +5795,7 @@
         <v>5</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5760,43 +5827,43 @@
         <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G30" t="n">
-        <v>0.658</v>
+        <v>0.646</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>39.5</v>
+        <v>39.4</v>
       </c>
       <c r="J30" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.493</v>
+        <v>0.492</v>
       </c>
       <c r="L30" t="n">
         <v>5.3</v>
       </c>
       <c r="M30" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="N30" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O30" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P30" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="R30" t="n">
         <v>10.6</v>
@@ -5808,13 +5875,13 @@
         <v>42</v>
       </c>
       <c r="U30" t="n">
-        <v>26.8</v>
+        <v>26.7</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
       </c>
       <c r="W30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>4.9</v>
@@ -5823,40 +5890,40 @@
         <v>5.4</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>104.5</v>
+        <v>104.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD30" t="n">
         <v>1</v>
       </c>
       <c r="AE30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH30" t="n">
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ30" t="n">
         <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL30" t="n">
         <v>23</v>
@@ -5877,10 +5944,10 @@
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5901,7 +5968,7 @@
         <v>25</v>
       </c>
       <c r="AZ30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA30" t="n">
         <v>5</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6024,7 @@
         <v>36.6</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
         <v>0.447</v>
@@ -5972,61 +6039,61 @@
         <v>0.348</v>
       </c>
       <c r="O31" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="P31" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
       </c>
       <c r="S31" t="n">
-        <v>29.9</v>
+        <v>29.8</v>
       </c>
       <c r="T31" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U31" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V31" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W31" t="n">
         <v>6</v>
       </c>
       <c r="X31" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y31" t="n">
         <v>5.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB31" t="n">
-        <v>96.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC31" t="n">
         <v>-4.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE31" t="n">
         <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH31" t="n">
         <v>11</v>
@@ -6035,7 +6102,7 @@
         <v>23</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>25</v>
@@ -6047,31 +6114,31 @@
         <v>23</v>
       </c>
       <c r="AN31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO31" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>14</v>
       </c>
       <c r="AR31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS31" t="n">
         <v>23</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU31" t="n">
         <v>30</v>
       </c>
       <c r="AV31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW31" t="n">
         <v>28</v>
@@ -6080,7 +6147,7 @@
         <v>11</v>
       </c>
       <c r="AY31" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ31" t="n">
         <v>21</v>
@@ -6089,7 +6156,7 @@
         <v>17</v>
       </c>
       <c r="BB31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC31" t="n">
         <v>26</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>4-9-2009-10</t>
+          <t>2010-04-09</t>
         </is>
       </c>
     </row>
